--- a/AAII_Financials/Quarterly/MXUBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MXUBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="92">
   <si>
     <t>MXUBY</t>
   </si>
@@ -656,75 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -764,8 +772,14 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -805,8 +819,14 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -846,8 +866,14 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,8 +889,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,8 +932,14 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,8 +979,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,8 +1026,14 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1027,8 +1073,14 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,8 +1093,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1082,8 +1136,14 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1123,8 +1183,14 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,8 +1206,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1181,8 +1249,14 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1222,8 +1296,14 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1263,8 +1343,14 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1304,8 +1390,14 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1345,8 +1437,14 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,8 +1484,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1427,8 +1531,14 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1468,8 +1578,14 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1625,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1672,14 @@
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1719,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,8 +1766,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1673,8 +1813,14 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1714,8 +1860,14 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,8 +1907,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1796,54 +1954,66 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +2029,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,377 +2048,433 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>887400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>873900</v>
+      </c>
+      <c r="F41" s="3">
         <v>1062100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1043500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1173300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1158300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>593900</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3">
         <v>792800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2045500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2014500</v>
+      </c>
+      <c r="F42" s="3">
         <v>1416400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1391600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>902200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>890700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>664700</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>110500</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F43" s="3">
         <v>37900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>37200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>41500</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
         <v>34300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>563600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>555000</v>
+      </c>
+      <c r="F44" s="3">
         <v>525100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>515900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>417600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>412300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>303500</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3">
         <v>314700</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>88900</v>
+      </c>
+      <c r="F45" s="3">
         <v>32700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>32100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>67700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>66900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>24700</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>23000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3597400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3542900</v>
+      </c>
+      <c r="F46" s="3">
         <v>3079600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3025600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2565800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2533100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1629800</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3">
         <v>1290100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>265900</v>
+      </c>
+      <c r="F47" s="3">
         <v>398500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>391500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>398200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>393100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>270400</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>44200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>888100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>874700</v>
+      </c>
+      <c r="F48" s="3">
         <v>843900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>829100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>806300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>796000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>780900</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3">
         <v>538300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E49" s="3">
         <v>37800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
+        <v>37800</v>
+      </c>
+      <c r="G49" s="3">
         <v>37100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>5800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>5800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>5700</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>3600</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2514,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,49 +2561,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>28500</v>
+      </c>
+      <c r="F52" s="3">
         <v>26000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>25500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>18800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>18500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>13100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
         <v>166000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,49 +2655,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4839600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4766200</v>
+      </c>
+      <c r="F54" s="3">
         <v>4402600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4325400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3809800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3761200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2710400</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3">
         <v>2058100</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2725,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,254 +2744,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>273800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>269600</v>
+      </c>
+      <c r="F57" s="3">
         <v>316300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>310800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>350000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>345600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>242100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>185700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F58" s="3">
         <v>14700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>14500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>8900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>8800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7100</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>46800</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>492400</v>
+      </c>
+      <c r="F59" s="3">
         <v>283500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>278600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>435400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>429900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>221200</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>169700</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>787600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>775700</v>
+      </c>
+      <c r="F60" s="3">
         <v>803700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>789600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>794300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>784200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>618800</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3">
         <v>526600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F61" s="3">
         <v>12100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>11900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5600</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>7700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F62" s="3">
         <v>4300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>4300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2800</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>8500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +3069,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +3116,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,49 +3163,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>855500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>842500</v>
+      </c>
+      <c r="F66" s="3">
         <v>861400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>846300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>825200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>814600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>647000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3">
         <v>563800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3233,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3276,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3323,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3034,8 +3370,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,49 +3417,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2967000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2922000</v>
+      </c>
+      <c r="F72" s="3">
         <v>2553200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2508500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2047000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2020900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1640100</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
         <v>1062600</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3511,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3558,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,49 +3605,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3935200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3875500</v>
+      </c>
+      <c r="F76" s="3">
         <v>3495500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3434200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2966300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2928400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2049000</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
         <v>1455200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1481800</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,54 +3699,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3408,8 +3798,14 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,29 +3821,31 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F83" s="3">
         <v>16300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>12900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>13000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>10600</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3466,8 +3864,14 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3911,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3958,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +4005,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +4052,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,49 +4099,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>150900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>148600</v>
+      </c>
+      <c r="F89" s="3">
         <v>197600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>194100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>228600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>225700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>124400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>194900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>196200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>99000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,49 +4169,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-27100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-26600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-21300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-21100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-33400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-51500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-51900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-52500</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4259,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,49 +4306,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-249100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-245300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-258900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-254400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-191400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-188900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-347000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-207500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-208900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>165300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,8 +4376,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3936,14 +4404,14 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>3</v>
+      <c r="M96" s="3">
+        <v>0</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>3</v>
@@ -3951,8 +4419,14 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4466,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4513,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,70 +4560,82 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-5200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-5100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>249700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>246500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-13000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-13100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1200</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-2900</v>
       </c>
       <c r="E101" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4156,45 +4654,57 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-103100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-101600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-69800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-68600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>284100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>280500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-225400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-25800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-26000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>262700</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>0</v>
       </c>
     </row>
